--- a/ig/nr-update-location-identifier/ValueSet-fr-core-related-person-role.xlsx
+++ b/ig/nr-update-location-identifier/ValueSet-fr-core-related-person-role.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE-R260-HL7Role" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from TRE-R217-Protect" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from TRE_R260-HL7Role" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from TRE_R217-Protect" r:id="rId5" sheetId="3"/>
     <sheet name="Include from contactRole2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-20T15:16:44+00:00</t>
+    <t>2023-12-20T16:57:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
